--- a/stories/arbres/ATOM-SEC.RUE.003-01.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami sort avec papa. Ils marchent dans la rue. Sami reste près de l'adulte. Il prend la main de papa. Il tient aussi le manteau. Main ou manteau. Papa dit : près de moi. Sami sent le manteau. Le manteau est doux. La main de papa est chaude. Sami marche à côté. Ils passent la boulangerie. Sami sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Papa sourit. Sami sourit aussi.</t>
+          <t>Sami sort avec papa. Ils marchent dans la rue. Sami reste près de l'adulte. Il prend la main de papa. Il tient aussi le manteau. Main ou manteau. Près de moi. Sami sent le manteau. Le manteau est doux. La main de papa est chaude. Sami marche à côté. Ils passent la boulangerie. Sami sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Papa sourit. Sami sourit aussi.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sami sort avec papa. Ils marchent dans la rue. Sami reste près de l'adulte. Il prend la main de papa. Il tient aussi le manteau. Main ou manteau.
+papa|Près de moi.
+narrateur|Sami sent le manteau. Le manteau est doux. La main de papa est chaude. Sami marche à côté. Ils passent la boulangerie. Sami sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Papa sourit. Sami sourit aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Sami marche dans la rue. Où est-il ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est près de papa. La main tient le manteau. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1840,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sami garde la main de papa. Ils rentrent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2007,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2047,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.003-01.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Sami sent le manteau. Le manteau est doux. La main de papa est chaude. Sami marche à côté. Ils passent la boulangerie. Sami sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Papa sourit. Sami sourit aussi.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Sami marche dans la rue. Où est-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Sami est près de papa. La main tient le manteau. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1845,6 +1853,7 @@
           <t>narrateur|Sami garde la main de papa. Ils rentrent à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2012,6 +2021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2054,6 +2064,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2255,6 +2279,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.003-01.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sami près de papa</t>
+          <t>La librairie jaune</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut voir le bateau dans la vitrine jaune. Un pigeon bat des ailes. Amir recule contre papa, reste près, main sur le manteau. Puis le bateau brille.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami sort avec papa. Ils marchent dans la rue. Sami reste près de l'adulte. Il prend la main de papa. Il tient aussi le manteau. Main ou manteau. Près de moi. Sami sent le manteau. Le manteau est doux. La main de papa est chaude. Sami marche à côté. Ils passent la boulangerie. Sami sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Papa sourit. Sami sourit aussi.</t>
+          <t>La façade jaune luit entre deux toits gris. Le soleil pose un carré sur le mur. Ça sent le papier et un peu de poussière. Un bateau peint dort derrière la vitre. La rue du village est calme. Amir vit ici, avec papa. Papa, la maison est jaune ! Oui. C'est la librairie. Tu as vu le bateau ? Il a une voile blanche. En ce moment, Amir prend le manteau. Le manteau de papa est laineux. Ils marchent tout près l'un de l'autre. Je veux voir le bateau ! On y va. Tu restes près de moi. Un pigeon gris picore une miette. Ses plumes brillent un peu. Le pigeon ! Il cherche du pain. Le pigeon bat des ailes, tout près. Ça fait un bruit de vent. Oh ! Amir recule contre papa. Son dos touche le manteau chaud. Tu es près de moi. Tu tiens le manteau ? Oui. Bravo. Le pigeon se pose sur un toit. Amir garde le tissu laineux. On reste près ? Oui, papa. La façade jaune est plus proche. Le bateau grossit dans la vitre. Tu marches à côté ? À côté. Leurs pieds vont ensemble. Le papier sent plus fort. Je vois la voile ! Merci d'être resté près. Amir serre encore le manteau. Le carré de soleil a bougé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sami sort avec papa. Ils marchent dans la rue. Sami reste &lt;emphasis level="moderate"&gt;près&lt;/emphasis&gt; de l'adulte. Il prend la main de papa. Il tient aussi le manteau. Main ou manteau. Papa dit : près de moi. Sami sent le manteau. Le manteau est doux. La main de papa est chaude. Sami marche à côté. Ils passent la boulangerie. Sami sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Papa sourit. Sami sourit aussi.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La façade jaune luit entre deux toits gris. Le soleil pose un carré sur le mur. Ça sent le papier et un peu de poussière. Un bateau peint dort derrière la vitre. La rue du village est calme. Amir vit ici, avec papa. Papa, la maison est jaune ! Oui. C'est la librairie. Tu as vu le bateau ? Il a une voile blanche. En ce moment, Amir prend le manteau. Le manteau de papa est laineux. Ils marchent tout près l'un de l'autre. Je veux voir le bateau ! On y va. Tu restes près de moi. Un pigeon gris picore une miette. Ses plumes brillent un peu. Le pigeon ! Il cherche du pain. Le pigeon bat des ailes, tout près. Ça fait un bruit de vent. Oh ! Amir recule contre papa. Son dos touche le manteau chaud. Tu es près de moi. Tu tiens le manteau ? Oui. Bravo. Le pigeon se pose sur un toit. Amir garde le tissu laineux. On reste près ? Oui, papa. La façade jaune est plus proche. Le bateau grossit dans la vitre. Tu marches à côté ? À côté. Leurs pieds vont ensemble. Le papier sent plus fort. Je vois la voile ! Merci d'être resté près. Amir serre encore le manteau. Le carré de soleil a bougé.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sami sort avec papa. Ils marchent dans la rue. Sami reste près de l'adulte. Il prend la main de papa. Il tient aussi le manteau. Main ou manteau.
-papa|Près de moi.
-narrateur|Sami sent le manteau. Le manteau est doux. La main de papa est chaude. Sami marche à côté. Ils passent la boulangerie. Sami sent le pain chaud. Il reste près de l'adulte. La main tient le manteau. Papa sourit. Sami sourit aussi.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La façade jaune luit entre deux toits gris.
+narrateur|Le soleil pose un carré sur le mur.
+narrateur|Ça sent le papier et un peu de poussière.
+narrateur|Un bateau peint dort derrière la vitre.
+narrateur|La rue du village est calme.
+narrateur|Amir vit ici, avec papa.
+enfant-m|Papa, la maison est jaune !
+papa|Oui.
+papa|C'est la librairie.
+papa|Tu as vu le bateau ?
+enfant-m|Il a une voile blanche.
+narrateur|En ce moment, Amir prend le manteau.
+narrateur|Le manteau de papa est laineux.
+narrateur|Ils marchent tout près l'un de l'autre.
+enfant-m|Je veux voir le bateau !
+papa|On y va.
+papa|Tu restes près de moi.
+narrateur|Un pigeon gris picore une miette.
+narrateur|Ses plumes brillent un peu.
+enfant-m|Le pigeon !
+papa|Il cherche du pain.
+narrateur|Le pigeon bat des ailes, tout près.
+narrateur|Ça fait un bruit de vent.
+enfant-m|Oh !
+narrateur|Amir recule contre papa.
+narrateur|Son dos touche le manteau chaud.
+papa|Tu es près de moi.
+papa|Tu tiens le manteau ?
+enfant-m|Oui.
+papa|Bravo.
+narrateur|Le pigeon se pose sur un toit.
+narrateur|Amir garde le tissu laineux.
+papa|On reste près ?
+enfant-m|Oui, papa.
+narrateur|La façade jaune est plus proche.
+narrateur|Le bateau grossit dans la vitre.
+papa|Tu marches à côté ?
+enfant-m|À côté.
+narrateur|Leurs pieds vont ensemble.
+narrateur|Le papier sent plus fort.
+enfant-m|Je vois la voile !
+papa|Merci d'être resté près.
+narrateur|Amir serre encore le manteau.
+narrateur|Le carré de soleil a bougé.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,12 +1399,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sami marche dans la rue. Où est-il ?</t>
+          <t>Amir marche dans la rue. Où est-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Sami marche dans la rue. Où est-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir marche dans la rue. Où est-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1362,7 +1419,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>près de papa | près | la main | manteau | à côté</t>
+          <t>près | près de papa | à côté | la main | le manteau | contre papa</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1377,7 +1434,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il reste près. Il tient la main. Où est Sami ?</t>
+          <t>Il reste près de papa. Où est Amir ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1426,7 +1483,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,10 +1559,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sami marche dans la rue. Où est-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir marche dans la rue.
+narrateur|Où est-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami est près de papa. La main tient le manteau. Papa est là.</t>
+          <t>Amir est près de papa. La main tient le manteau. Il a reculé contre papa. Tu es resté près de moi ? Oui. J'ai tenu le manteau. Bravo, Amir. Près de moi. Le manteau laineux reste doux. Le pigeon roucoule sur le toit. La vitre jaune est tout près.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Sami est &lt;emphasis level="moderate"&gt;près&lt;/emphasis&gt; de papa. La main tient le manteau. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir est près de papa. La main tient le manteau. Il a reculé contre papa. Tu es resté près de moi ? Oui. J'ai tenu le manteau. Bravo, Amir. Près de moi. Le manteau laineux reste doux. Le pigeon roucoule sur le toit. La vitre jaune est tout près.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1591,14 +1648,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,10 +1735,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sami est près de papa. La main tient le manteau. Papa est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir est près de papa.
+narrateur|La main tient le manteau.
+narrateur|Il a reculé contre papa.
+papa|Tu es resté près de moi ?
+enfant-m|Oui.
+enfant-m|J'ai tenu le manteau.
+papa|Bravo, Amir.
+papa|Près de moi.
+narrateur|Le manteau laineux reste doux.
+narrateur|Le pigeon roucoule sur le toit.
+narrateur|La vitre jaune est tout près.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1706,12 +1772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sami garde la main de papa. Ils rentrent à la maison.</t>
+          <t>Ils s'arrêtent devant la librairie. Tu vois le bateau ? Amir pose le nez sur la vitre. La voile est blanche ! Oui. Tu es resté près. Le verre est un peu froid. Le bateau a une petite ancre. Il peut flotter ? Dans l'histoire, oui. Amir garde le manteau d'une main. De l'autre, il montre le bateau. Le soleil chauffe le mur jaune. C'est tout chaud ! Oui. On rentre près l'un de l'autre. Le pigeon a trouvé sa miette. La poussière danse dans le carré jaune.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Sami garde la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Ils rentrent à la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils s'arrêtent devant la librairie. Tu vois le bateau ? Amir pose le nez sur la vitre. La voile est blanche ! Oui. Tu es resté près. Le verre est un peu froid. Le bateau a une petite ancre. Il peut flotter ? Dans l'histoire, oui. Amir garde le manteau d'une main. De l'autre, il montre le bateau. Le soleil chauffe le mur jaune. C'est tout chaud ! Oui. On rentre près l'un de l'autre. Le pigeon a trouvé sa miette. La poussière danse dans le carré jaune.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,14 +1833,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1850,10 +1916,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sami garde la main de papa. Ils rentrent à la maison.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils s'arrêtent devant la librairie.
+papa|Tu vois le bateau ?
+narrateur|Amir pose le nez sur la vitre.
+enfant-m|La voile est blanche !
+papa|Oui.
+papa|Tu es resté près.
+narrateur|Le verre est un peu froid.
+narrateur|Le bateau a une petite ancre.
+enfant-m|Il peut flotter ?
+papa|Dans l'histoire, oui.
+narrateur|Amir garde le manteau d'une main.
+narrateur|De l'autre, il montre le bateau.
+narrateur|Le soleil chauffe le mur jaune.
+enfant-m|C'est tout chaud !
+papa|Oui.
+papa|On rentre près l'un de l'autre.
+narrateur|Le pigeon a trouvé sa miette.
+narrateur|La poussière danse dans le carré jaune.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1878,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai vu le bateau. Oui. Merci d'être resté près. Le mur jaune reste chaud. Le bateau du livre brille dans le soleil jaune.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai vu le bateau. Oui. Merci d'être resté près. Le mur jaune reste chaud. Le bateau du livre brille dans le soleil jaune.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,14 +2021,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2100,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|J'ai vu le bateau.
+papa|Oui.
+papa|Merci d'être resté près.
+narrateur|Le mur jaune reste chaud.
+narrateur|Le bateau du livre brille dans le soleil jaune.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2040,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2163,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.003-01.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.003-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rue près de la maison</t>
+          <t>rue du village vers la librairie jaune</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sami, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
